--- a/data/BS Data.xlsx
+++ b/data/BS Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4a1321f4e8289/Desktop/Banking Stuff/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="629" documentId="13_ncr:1_{1E316B21-B76B-4A01-92C1-8C4D963F0276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{694D2C84-9DB6-4671-A50B-D1CF93CEF7E2}"/>
+  <xr:revisionPtr revIDLastSave="260" documentId="8_{3A1686BD-CA46-40DD-BF82-F05E2E7E6059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9244EC97-699A-4828-BDAF-8902D65D3D47}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{05B6BE92-3596-44ED-96C8-DB73E0EEA56B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{05B6BE92-3596-44ED-96C8-DB73E0EEA56B}"/>
   </bookViews>
   <sheets>
     <sheet name="Societies" sheetId="3" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="1174">
   <si>
     <t>Building Society Name</t>
   </si>
@@ -1961,9 +1961,6 @@
     <t>britannia.jpeg</t>
   </si>
   <si>
-    <t>2009-2013 (As part of The Co-operative Bank): britannia-2009.jpg, 1995-2008: britannia.jpeg, Until 1995: britannia-1995.png</t>
-  </si>
-  <si>
     <t>glantawe-permanent.jpg</t>
   </si>
   <si>
@@ -2285,15 +2282,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Santander (Demutualised)</t>
-  </si>
-  <si>
-    <t>Halifax (Demutualised)</t>
-  </si>
-  <si>
-    <t>Barclays (Demutualised)</t>
-  </si>
-  <si>
     <t>#004C45</t>
   </si>
   <si>
@@ -2327,9 +2315,6 @@
     <t>#1E7560</t>
   </si>
   <si>
-    <t>#FEF0D9</t>
-  </si>
-  <si>
     <t>#182745</t>
   </si>
   <si>
@@ -2384,9 +2369,6 @@
     <t>#EB600A</t>
   </si>
   <si>
-    <t>#FFEDDD</t>
-  </si>
-  <si>
     <t>#007E36</t>
   </si>
   <si>
@@ -2406,9 +2388,6 @@
   </si>
   <si>
     <t>#EC0000</t>
-  </si>
-  <si>
-    <t>#005EB8</t>
   </si>
   <si>
     <t>#00AEEF</t>
@@ -3168,9 +3147,6 @@
 1956 Bristol &amp; West Advert on Express and Echo: provident-permanent-1956-advert.png</t>
   </si>
   <si>
-    <t>Kent Reliance/OneSavings Bank (Confusion?)</t>
-  </si>
-  <si>
     <t>reading-high-wycombe.png</t>
   </si>
   <si>
@@ -3492,9 +3468,6 @@
     <t>West London Building Society was established in 1850 as West London Permanent Mutual Benefit Building Society. Following renamings in 1961 and 1963, it transferred its engagements to Bristol &amp; West Building Society in 1974 and is now part of Coventry Building Society.</t>
   </si>
   <si>
-    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk</t>
-  </si>
-  <si>
     <t>farmers-general-investment.png</t>
   </si>
   <si>
@@ -3508,6 +3481,261 @@
   </si>
   <si>
     <t>partial transfer</t>
+  </si>
+  <si>
+    <t>landore.png</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive (Logo) https://www.britishnewspaperarchive.co.uk/viewer/BL/0004705/19500511/005/0005?browse=False, British Newspaper Archive (Advert)  https://www.britishnewspaperarchive.co.uk/viewer/BL/0004705/19500209/005/0005?browse=False</t>
+  </si>
+  <si>
+    <t>Landore Building Society was established in 1875, and was renamed to South West Wales Building Society in 1963. It transferred its engagements to Bristol &amp; West Building Society in 1977.
+1950 Advert on South Wales Daily Post: landore-1950-advert.png</t>
+  </si>
+  <si>
+    <t>~1879</t>
+  </si>
+  <si>
+    <t>national-emblem-permanent.png</t>
+  </si>
+  <si>
+    <t>National Emblem Permanent Building Society was established around 1879. It transferred its engagements to Clydach Permanent Benefit Building Society in 1944.</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk/viewer/BL/0000903/19101001/060/0004?browse=False</t>
+  </si>
+  <si>
+    <t>swansea-imperial-permanent.png</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk/viewer/BL/0004705/19330317/004/0004?browse=False</t>
+  </si>
+  <si>
+    <t>Clydach Permanent Benefit Building Society accepted a transfer of engagements from National Emblem Permanent Building Society in 1944. It then transferred its engagements to South West Wales Building Society in 1968.</t>
+  </si>
+  <si>
+    <t>South West Wales Building Society was established as Landore Building Society in 1875, and was renamed in 1963. It accepted transfers of engagement from three local building societies before transferring its engagements to Bristol &amp; West Building Society in 1977.</t>
+  </si>
+  <si>
+    <t>Swansea Imperial Permanent Building Society was established in 1878. In 1968 it transferred its engagements to South West Wales Building Society.</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk/viewer/BL/0004705/19480207/004/0004?browse=False</t>
+  </si>
+  <si>
+    <t>swansea-rock-permanent.png</t>
+  </si>
+  <si>
+    <t>Swansea Rock Permanent Building Society was established in 1877. In 1970 it transferred its engagements to South West Wales Building Society.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wilchester Permanent Building Society transferred its engagements to Bristol &amp; West Building Society in 1978. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Little information about this society is available in surviving records.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Town &amp; County of Poole Building Society was established around 1878 and went by Poole Building Society before officially being renamed as such in 1951. In 1979 it transferred its engagements to Bristol &amp; West in 1979.</t>
+  </si>
+  <si>
+    <t>Founded around 1878, Poole Building Society was the name used by Town &amp; County of Poole Building Society for several decades before being officially renamed in 1951. In 1979 it transferred its engagements to Bristol &amp; West in 1979.</t>
+  </si>
+  <si>
+    <t>cheshunt-permanent-benefit.png</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk/viewer/bl/0000756/19390421/154/0005</t>
+  </si>
+  <si>
+    <t>Cheshunt Permanent Benefit Building Society was established in 1861, and was renamed to Cheshunt Building Society in 1951. In 1991 it transferred its engagements to Bristol &amp; West Building Soociety.</t>
+  </si>
+  <si>
+    <t>Cheshunt Building Society was established in 1861 as Cheshunt Permanent Benefit Building Society before being renamed in 1951.  In 1991 it transferred its engagements to Bristol &amp; West Building Soociety.</t>
+  </si>
+  <si>
+    <t>cheshunt.png</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk/viewer/BL/0003617/19870313/044/0044?browse=False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darlington </t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>Cumberland Building Society</t>
+  </si>
+  <si>
+    <t>Cumberland Co-operative Benefit Building Society</t>
+  </si>
+  <si>
+    <t>Cumbria Building Society</t>
+  </si>
+  <si>
+    <t>Workington &amp; West Cumberland Building Society</t>
+  </si>
+  <si>
+    <t>Workington &amp; West Cumberland Permanent Building Society</t>
+  </si>
+  <si>
+    <t>cumberland</t>
+  </si>
+  <si>
+    <t>cumberland-co-operative-benefit</t>
+  </si>
+  <si>
+    <t>cumbria</t>
+  </si>
+  <si>
+    <t>workington-west-cumberland</t>
+  </si>
+  <si>
+    <t>workington-west-cumberland-permanent</t>
+  </si>
+  <si>
+    <t>Cumbria</t>
+  </si>
+  <si>
+    <t>Cumberland Co-op</t>
+  </si>
+  <si>
+    <t>Workington &amp; West Cumberland</t>
+  </si>
+  <si>
+    <t>Workington &amp; West Cumberland Permanent</t>
+  </si>
+  <si>
+    <t>general-thrift-permanent.png</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/,  (1948 Logo) https://www.britishnewspaperarchive.co.uk/viewer/BL/0004648/19481230/167/0006?browse=False, British Newspaper Archive (1967 Advert) https://www.britishnewspaperarchive.co.uk/viewer/BL/0001984/19670303/173/0004?browse=False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrift Building Society was established as General Thrift Permanent Building Society in 1886, and was renamed in 1979. In 1987 it transferred its engagements to Bristol &amp; West Building Society. </t>
+  </si>
+  <si>
+    <t>General Thrift Permanent Building Society was established in 1886 and was renamed to Thrift Building Society in 1979. In 1987 it transferred its engagements to Bristol &amp; West Building Society. 
+1967 Advert on Fulham Chronicle: general-thrift-permanent-1967-advert.png</t>
+  </si>
+  <si>
+    <t>#F9AF3C</t>
+  </si>
+  <si>
+    <t>#71A8A0</t>
+  </si>
+  <si>
+    <t>OneSavings Bank (Kent Reliance)</t>
+  </si>
+  <si>
+    <t>Barclays - Woolwich</t>
+  </si>
+  <si>
+    <t>Santander - Abbey National, Alliance &amp; Leicester, Bradford &amp; Bingley</t>
+  </si>
+  <si>
+    <t>Lloyds - Halifax, Cheltenham &amp; Gloucester</t>
+  </si>
+  <si>
+    <t>#11B67A</t>
+  </si>
+  <si>
+    <t>Aid to Thrift Building Society was established around 1884, and transferred its engagements to Bristol &amp; West Building Society in 1988.</t>
+  </si>
+  <si>
+    <t>aid-to-thrift.png</t>
+  </si>
+  <si>
+    <t>Building Societies Association https://www.bsa.org.uk/, British Newspaper Archive https://www.britishnewspaperarchive.co.uk/viewer/bl/0004650/18850228/027/0002</t>
+  </si>
+  <si>
+    <t>Darlington Equitable Building Society</t>
+  </si>
+  <si>
+    <t>Darlington Building Society</t>
+  </si>
+  <si>
+    <t>Earl Shilton Building Society</t>
+  </si>
+  <si>
+    <t>Ecology Building Society</t>
+  </si>
+  <si>
+    <t>Durham &amp; Yorkshire Building Society</t>
+  </si>
+  <si>
+    <t>Advance Building Society</t>
+  </si>
+  <si>
+    <t>Earl Shilton Permanent Benefit Building &amp; Land Society</t>
+  </si>
+  <si>
+    <t>darlington</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>darlington-equitable</t>
+  </si>
+  <si>
+    <t>durham-yorkshire</t>
+  </si>
+  <si>
+    <t>earl-shilton</t>
+  </si>
+  <si>
+    <t>advance</t>
+  </si>
+  <si>
+    <t>earl-shilton-permanent-benefit</t>
+  </si>
+  <si>
+    <t>Advance</t>
+  </si>
+  <si>
+    <t>Darlington Equitable</t>
+  </si>
+  <si>
+    <t>Durham &amp; Yorkshire</t>
+  </si>
+  <si>
+    <t>Earl Shilton Permanent Benefit</t>
+  </si>
+  <si>
+    <t>2009-2013 (As part of The Co-operative Bank): britannia-2009.jpg, 1995-2008: britannia.jpeg, Until 1995: britannia-1995.jpg</t>
+  </si>
+  <si>
+    <t>cumberland.png</t>
+  </si>
+  <si>
+    <t>darlington.svg</t>
+  </si>
+  <si>
+    <t>earl-shilton.png</t>
+  </si>
+  <si>
+    <t>ecology.png</t>
   </si>
 </sst>
 </file>
@@ -3569,7 +3797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3584,9 +3812,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4131,14 +4356,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A39B9A56-4599-49B5-AFB6-7F87FAFB13F2}" name="Table13" displayName="Table13" ref="A1:O172" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
-  <autoFilter ref="A1:O172" xr:uid="{3CE666DD-2EB1-43D8-B766-F27F8BA2564C}">
-    <filterColumn colId="14">
-      <filters blank="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A39B9A56-4599-49B5-AFB6-7F87FAFB13F2}" name="Table13" displayName="Table13" ref="A1:O183" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+  <autoFilter ref="A1:O183" xr:uid="{3CE666DD-2EB1-43D8-B766-F27F8BA2564C}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Bath"/>
+        <filter val="Beverley"/>
+        <filter val="Buckinghamshire"/>
+        <filter val="Cambridge"/>
+        <filter val="Chorley"/>
+        <filter val="Coventry"/>
+      </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O172">
-    <sortCondition ref="E1:E172"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O183">
+    <sortCondition ref="D1:D183"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="5" xr3:uid="{BEAACFE7-CBDA-4FAD-9873-54AFEAEDAB04}" name="ID" dataDxfId="26"/>
@@ -4162,8 +4394,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2698B95E-507A-4E66-BEEB-203BFCB2C641}" name="Table134" displayName="Table134" ref="A1:E165" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:E165" xr:uid="{3CE666DD-2EB1-43D8-B766-F27F8BA2564C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2698B95E-507A-4E66-BEEB-203BFCB2C641}" name="Table134" displayName="Table134" ref="A1:E173" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:E173" xr:uid="{3CE666DD-2EB1-43D8-B766-F27F8BA2564C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D120">
     <sortCondition ref="B1:B120"/>
   </sortState>
@@ -4510,7 +4742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745FDB81-20CC-46E9-B9EB-CBF52F074379}">
-  <dimension ref="A1:O172"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr defaultColWidth="35" defaultRowHeight="58.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="17.54296875" style="2" customWidth="1"/>
@@ -4570,7 +4802,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>191</v>
       </c>
@@ -4607,10 +4839,10 @@
         <v>402</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>192</v>
       </c>
@@ -4647,10 +4879,10 @@
         <v>413</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>180</v>
       </c>
@@ -4688,10 +4920,10 @@
         <v>287</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -4727,10 +4959,10 @@
         <v>420</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>183</v>
       </c>
@@ -4767,10 +4999,10 @@
         <v>422</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>127</v>
       </c>
@@ -4806,10 +5038,10 @@
         <v>419</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>195</v>
       </c>
@@ -4846,10 +5078,10 @@
         <v>421</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>128</v>
       </c>
@@ -4885,10 +5117,10 @@
         <v>427</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>186</v>
       </c>
@@ -4925,10 +5157,10 @@
         <v>428</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>196</v>
       </c>
@@ -4966,24 +5198,27 @@
         <v>425</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1884</v>
       </c>
       <c r="H12" s="2">
         <v>1988</v>
@@ -4992,27 +5227,35 @@
         <v>121</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>1148</v>
+      </c>
       <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N12" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="O12" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G13" s="2">
         <v>1851</v>
@@ -5025,34 +5268,34 @@
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="O13" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G14" s="2">
         <v>1879</v>
@@ -5065,34 +5308,34 @@
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
       <c r="O14" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G15" s="2">
         <v>1862</v>
@@ -5105,34 +5348,34 @@
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
       <c r="O15" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G16" s="2">
         <v>1925</v>
@@ -5141,40 +5384,40 @@
         <v>1997</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="O16" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G17" s="2">
         <v>1850</v>
@@ -5187,34 +5430,34 @@
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="O17" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G18" s="2">
         <v>1866</v>
@@ -5227,34 +5470,34 @@
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="O18" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G19" s="2">
         <v>1971</v>
@@ -5268,7 +5511,7 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3" t="s">
@@ -5278,21 +5521,21 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G20" s="2">
         <v>1849</v>
@@ -5305,14 +5548,14 @@
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="O20" s="5">
         <v>46150</v>
@@ -5320,21 +5563,21 @@
     </row>
     <row r="21" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="G21" s="6">
+        <v>977</v>
+      </c>
+      <c r="G21" s="2">
         <v>1951</v>
       </c>
       <c r="H21" s="2">
@@ -5344,27 +5587,38 @@
         <v>121</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1118</v>
+      </c>
       <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
+      <c r="N21" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="O21" s="5">
+        <v>46151</v>
+      </c>
     </row>
     <row r="22" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1861</v>
       </c>
       <c r="H22" s="2">
         <v>1951</v>
@@ -5373,27 +5627,35 @@
         <v>122</v>
       </c>
       <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1117</v>
+      </c>
       <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N22" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="O22" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G23" s="2">
         <v>1908</v>
@@ -5407,11 +5669,11 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="O23" s="5">
         <v>46149</v>
@@ -5419,19 +5681,19 @@
     </row>
     <row r="24" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="H24" s="2">
         <v>1968</v>
@@ -5439,30 +5701,36 @@
       <c r="I24" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="L24" s="3" t="s">
+        <v>1106</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>553</v>
+      </c>
+      <c r="O24" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G25" s="2">
         <v>1853</v>
@@ -5475,34 +5743,34 @@
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="O25" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G26" s="2">
         <v>1964</v>
@@ -5515,34 +5783,34 @@
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="O26" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G27" s="2">
         <v>1847</v>
@@ -5555,34 +5823,34 @@
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="O27" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="H28" s="2">
         <v>1955</v>
@@ -5595,7 +5863,7 @@
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3" t="s">
@@ -5605,21 +5873,21 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="H29" s="2">
         <v>1971</v>
@@ -5631,34 +5899,34 @@
         <v>143</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="O29" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G30" s="2">
         <v>1857</v>
@@ -5671,34 +5939,34 @@
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="O30" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G31" s="2">
         <v>1865</v>
@@ -5711,14 +5979,14 @@
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="O31" s="5">
         <v>46148</v>
@@ -5726,19 +5994,22 @@
     </row>
     <row r="32" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1886</v>
       </c>
       <c r="H32" s="2">
         <v>1979</v>
@@ -5747,27 +6018,35 @@
         <v>122</v>
       </c>
       <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>1140</v>
+      </c>
       <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N32" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="O32" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G33" s="2">
         <v>1964</v>
@@ -5781,31 +6060,31 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="O33" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G34" s="2">
         <v>1861</v>
@@ -5818,14 +6097,14 @@
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="2" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="O34" s="5">
         <v>46148</v>
@@ -5833,19 +6112,22 @@
     </row>
     <row r="35" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1875</v>
       </c>
       <c r="H35" s="2">
         <v>1963</v>
@@ -5854,29 +6136,38 @@
         <v>122</v>
       </c>
       <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>1099</v>
+      </c>
       <c r="M35" s="3"/>
       <c r="N35" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O35" s="5"/>
+        <v>1098</v>
+      </c>
+      <c r="O35" s="5">
+        <v>46151</v>
+      </c>
     </row>
     <row r="36" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>1100</v>
       </c>
       <c r="H36" s="2">
         <v>1944</v>
@@ -5885,29 +6176,35 @@
         <v>121</v>
       </c>
       <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>1102</v>
+      </c>
       <c r="M36" s="3"/>
       <c r="N36" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1103</v>
+      </c>
+      <c r="O36" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G37" s="2">
         <v>1864</v>
@@ -5920,34 +6217,34 @@
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="M37" s="3"/>
       <c r="N37" s="3" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
       <c r="O37" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G38" s="2">
         <v>1962</v>
@@ -5960,34 +6257,34 @@
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
       <c r="O38" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G39" s="2">
         <v>1884</v>
@@ -6000,34 +6297,34 @@
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
       <c r="O39" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G40" s="2">
         <v>1875</v>
@@ -6040,14 +6337,14 @@
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="O40" s="5">
         <v>46150</v>
@@ -6055,19 +6352,19 @@
     </row>
     <row r="41" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>984</v>
       </c>
       <c r="G41" s="2">
         <v>1951</v>
@@ -6080,26 +6377,32 @@
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="L41" s="3" t="s">
+        <v>1114</v>
+      </c>
       <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N41" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="O41" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G42" s="2">
         <v>1849</v>
@@ -6112,34 +6415,34 @@
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="M42" s="3"/>
       <c r="N42" s="3" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="O42" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G43" s="2">
         <v>1852</v>
@@ -6152,34 +6455,34 @@
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="M43" s="3"/>
       <c r="N43" s="3" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="O43" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G44" s="2">
         <v>1948</v>
@@ -6192,34 +6495,34 @@
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="O44" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G45" s="2">
         <v>1865</v>
@@ -6232,34 +6535,34 @@
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="O45" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G46" s="2">
         <v>1853</v>
@@ -6272,34 +6575,34 @@
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="O46" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G47" s="2">
         <v>1962</v>
@@ -6312,34 +6615,34 @@
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="3" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="O47" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G48" s="2">
         <v>1849</v>
@@ -6352,34 +6655,34 @@
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="O48" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G49" s="2">
         <v>1944</v>
@@ -6393,7 +6696,7 @@
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3" t="s">
@@ -6403,21 +6706,21 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G50" s="2">
         <v>1891</v>
@@ -6430,14 +6733,14 @@
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="O50" s="5">
         <v>46149</v>
@@ -6445,19 +6748,19 @@
     </row>
     <row r="51" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G51" s="2">
         <v>1963</v>
@@ -6470,28 +6773,32 @@
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="L51" s="3" t="s">
+        <v>1107</v>
+      </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O51" s="5"/>
-    </row>
-    <row r="52" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>553</v>
+      </c>
+      <c r="O51" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G52" s="2">
         <v>1955</v>
@@ -6504,14 +6811,14 @@
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="O52" s="5">
         <v>46149</v>
@@ -6519,19 +6826,22 @@
     </row>
     <row r="53" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1878</v>
       </c>
       <c r="H53" s="2">
         <v>1968</v>
@@ -6540,29 +6850,38 @@
         <v>121</v>
       </c>
       <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
+      <c r="K53" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>1108</v>
+      </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O53" s="5"/>
+        <v>1105</v>
+      </c>
+      <c r="O53" s="5">
+        <v>46151</v>
+      </c>
     </row>
     <row r="54" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1877</v>
       </c>
       <c r="H54" s="2">
         <v>1970</v>
@@ -6571,29 +6890,35 @@
         <v>121</v>
       </c>
       <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
+      <c r="K54" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>1111</v>
+      </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="O54" s="5"/>
-    </row>
-    <row r="55" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1109</v>
+      </c>
+      <c r="O54" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G55" s="2">
         <v>1859</v>
@@ -6606,14 +6931,14 @@
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>1005</v>
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="O55" s="5">
         <v>46148</v>
@@ -6621,19 +6946,19 @@
     </row>
     <row r="56" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G56" s="2">
         <v>1979</v>
@@ -6646,26 +6971,35 @@
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
+      <c r="L56" s="3" t="s">
+        <v>1139</v>
+      </c>
       <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
+      <c r="N56" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="O56" s="5">
+        <v>46151</v>
+      </c>
     </row>
     <row r="57" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
+      </c>
+      <c r="G57" s="2">
+        <v>1878</v>
       </c>
       <c r="H57" s="2">
         <v>1951</v>
@@ -6675,26 +7009,32 @@
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
+      <c r="L57" s="3" t="s">
+        <v>1113</v>
+      </c>
       <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N57" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="O57" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G58" s="2">
         <v>1879</v>
@@ -6707,34 +7047,34 @@
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="M58" s="3"/>
       <c r="N58" s="3" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="O58" s="5">
         <v>46149</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G59" s="2">
         <v>1880</v>
@@ -6747,34 +7087,34 @@
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>999</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>1006</v>
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="O59" s="5">
         <v>46148</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G60" s="2">
         <v>1963</v>
@@ -6787,34 +7127,34 @@
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="O60" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G61" s="2">
         <v>1961</v>
@@ -6827,34 +7167,34 @@
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="3" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
       <c r="O61" s="5">
         <v>46150</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="G62" s="2">
         <v>1850</v>
@@ -6867,14 +7207,14 @@
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="M62" s="3"/>
       <c r="N62" s="3" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="O62" s="5">
         <v>46150</v>
@@ -6882,19 +7222,19 @@
     </row>
     <row r="63" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="H63" s="2">
         <v>1978</v>
@@ -6902,22 +7242,30 @@
       <c r="I63" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J63" s="3"/>
+      <c r="J63" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
+      <c r="L63" s="3" t="s">
+        <v>1112</v>
+      </c>
       <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N63" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="O63" s="5">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>7</v>
@@ -6926,43 +7274,41 @@
         <v>153</v>
       </c>
       <c r="F64" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G64" s="2">
-        <v>1976</v>
+        <v>1962</v>
       </c>
       <c r="H64" s="2">
-        <v>1991</v>
+        <v>1981</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>813</v>
+        <v>633</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>814</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="M64" s="3"/>
       <c r="N64" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="O64" s="5">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>641</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>296</v>
+        <v>370</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>7</v>
@@ -6970,44 +7316,39 @@
       <c r="E65" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F65" s="2">
-        <v>3</v>
-      </c>
       <c r="G65" s="2">
+        <v>1866</v>
+      </c>
+      <c r="H65" s="2">
         <v>1962</v>
       </c>
-      <c r="H65" s="2">
-        <v>1986</v>
-      </c>
       <c r="I65" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>791</v>
+        <v>632</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>634</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="M65" s="3"/>
       <c r="N65" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="O65" s="5">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>640</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>399</v>
+        <v>296</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>7</v>
@@ -7016,41 +7357,43 @@
         <v>153</v>
       </c>
       <c r="F66" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" s="2">
         <v>1962</v>
       </c>
       <c r="H66" s="2">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>823</v>
+        <v>784</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="M66" s="3"/>
+        <v>787</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>634</v>
+      </c>
       <c r="N66" s="3" t="s">
-        <v>824</v>
+        <v>785</v>
       </c>
       <c r="O66" s="5">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>47</v>
+        <v>783</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>7</v>
@@ -7058,42 +7401,39 @@
       <c r="E67" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F67" s="2">
-        <v>5</v>
-      </c>
-      <c r="G67" s="2">
+      <c r="G67" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="H67" s="2">
         <v>1962</v>
       </c>
-      <c r="H67" s="2">
-        <v>1982</v>
-      </c>
       <c r="I67" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3" t="s">
-        <v>821</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>818</v>
+        <v>786</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3" t="s">
-        <v>822</v>
+        <v>788</v>
       </c>
       <c r="O67" s="5">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>156</v>
+        <v>827</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>308</v>
+        <v>876</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>33</v>
+        <v>876</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -7102,41 +7442,41 @@
         <v>153</v>
       </c>
       <c r="F68" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2">
-        <v>1967</v>
+        <v>1997</v>
       </c>
       <c r="H68" s="2">
-        <v>1982</v>
+        <v>2005</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>121</v>
+        <v>979</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3" t="s">
-        <v>807</v>
+        <v>984</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>631</v>
+        <v>981</v>
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3" t="s">
-        <v>808</v>
+        <v>989</v>
       </c>
       <c r="O68" s="5">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>292</v>
+        <v>377</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>7</v>
@@ -7145,41 +7485,41 @@
         <v>153</v>
       </c>
       <c r="F69" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G69" s="2">
-        <v>1962</v>
+        <v>1886</v>
       </c>
       <c r="H69" s="2">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3" t="s">
         <v>642</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -7188,39 +7528,43 @@
         <v>153</v>
       </c>
       <c r="F70" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G70" s="2">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H70" s="2">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
+      <c r="K70" s="3" t="s">
+        <v>792</v>
+      </c>
       <c r="L70" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="M70" s="3"/>
+        <v>789</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>790</v>
+      </c>
       <c r="N70" s="3" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="O70" s="5">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>267</v>
+        <v>135</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>344</v>
+        <v>307</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>7</v>
@@ -7229,41 +7573,39 @@
         <v>153</v>
       </c>
       <c r="F71" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G71" s="2">
-        <v>1878</v>
+        <v>1865</v>
       </c>
       <c r="H71" s="2">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J71" s="3"/>
-      <c r="K71" s="3" t="s">
-        <v>830</v>
-      </c>
+      <c r="K71" s="3"/>
       <c r="L71" s="3" t="s">
-        <v>831</v>
+        <v>796</v>
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3" t="s">
-        <v>832</v>
+        <v>797</v>
       </c>
       <c r="O71" s="5">
         <v>46147</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>7</v>
@@ -7272,43 +7614,41 @@
         <v>153</v>
       </c>
       <c r="F72" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G72" s="2">
-        <v>1866</v>
+        <v>1967</v>
       </c>
       <c r="H72" s="2">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>797</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="M72" s="3"/>
       <c r="N72" s="3" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="O72" s="5">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>7</v>
@@ -7316,34 +7656,31 @@
       <c r="E73" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="2">
-        <v>11</v>
-      </c>
       <c r="G73" s="2">
-        <v>1852</v>
+        <v>1865</v>
       </c>
       <c r="H73" s="2">
-        <v>1980</v>
+        <v>1967</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3" t="s">
-        <v>639</v>
+        <v>798</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>799</v>
+      </c>
+      <c r="O73" s="5">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>216</v>
       </c>
@@ -7373,28 +7710,28 @@
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>625</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>369</v>
+        <v>315</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>7</v>
@@ -7403,41 +7740,41 @@
         <v>153</v>
       </c>
       <c r="F75" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2">
-        <v>1907</v>
+        <v>1974</v>
       </c>
       <c r="H75" s="2">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>626</v>
+        <v>585</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3" t="s">
-        <v>646</v>
+        <v>620</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>377</v>
+        <v>319</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>7</v>
@@ -7446,41 +7783,43 @@
         <v>153</v>
       </c>
       <c r="F76" s="2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G76" s="2">
-        <v>1886</v>
+        <v>1976</v>
       </c>
       <c r="H76" s="2">
-        <v>1977</v>
+        <v>1991</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="3" t="s">
-        <v>635</v>
+        <v>806</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="M76" s="3"/>
+        <v>808</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>807</v>
+      </c>
       <c r="N76" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>809</v>
+      </c>
+      <c r="O76" s="5">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>7</v>
@@ -7488,42 +7827,41 @@
       <c r="E77" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F77" s="2">
-        <v>15</v>
-      </c>
       <c r="G77" s="2">
-        <v>1974</v>
+        <v>1866</v>
       </c>
       <c r="H77" s="2">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>122</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3" t="s">
-        <v>608</v>
+        <v>803</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="M77" s="3"/>
+        <v>802</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>804</v>
+      </c>
       <c r="N77" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="O77" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>805</v>
+      </c>
+      <c r="O77" s="5">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>370</v>
+        <v>327</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>7</v>
@@ -7531,39 +7869,42 @@
       <c r="E78" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="F78" s="2">
+        <v>5</v>
+      </c>
       <c r="G78" s="2">
-        <v>1866</v>
+        <v>1962</v>
       </c>
       <c r="H78" s="2">
-        <v>1962</v>
+        <v>1982</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3" t="s">
-        <v>632</v>
+        <v>814</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>628</v>
+        <v>811</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>815</v>
+      </c>
+      <c r="O78" s="5">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>790</v>
+        <v>105</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>7</v>
@@ -7571,8 +7912,8 @@
       <c r="E79" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>788</v>
+      <c r="G79" s="2">
+        <v>1869</v>
       </c>
       <c r="H79" s="2">
         <v>1962</v>
@@ -7580,30 +7921,30 @@
       <c r="I79" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J79" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="K79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3" t="s">
+        <v>813</v>
+      </c>
       <c r="L79" s="3" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
       <c r="O79" s="5">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>834</v>
+        <v>257</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>883</v>
+        <v>364</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>883</v>
+        <v>74</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>7</v>
@@ -7612,41 +7953,41 @@
         <v>153</v>
       </c>
       <c r="F80" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G80" s="2">
-        <v>1997</v>
+        <v>1852</v>
       </c>
       <c r="H80" s="2">
-        <v>2005</v>
+        <v>1980</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>986</v>
+        <v>121</v>
       </c>
       <c r="J80" s="3"/>
       <c r="K80" s="3" t="s">
-        <v>991</v>
+        <v>638</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>988</v>
+        <v>627</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3" t="s">
-        <v>996</v>
-      </c>
-      <c r="O80" s="5">
-        <v>46148</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>644</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>91</v>
+        <v>819</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>7</v>
@@ -7655,38 +7996,38 @@
         <v>153</v>
       </c>
       <c r="G81" s="2">
-        <v>1865</v>
+        <v>1857</v>
       </c>
       <c r="H81" s="2">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>122</v>
       </c>
       <c r="J81" s="3"/>
       <c r="K81" s="3" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>630</v>
+        <v>822</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="O81" s="5">
         <v>46147</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>320</v>
+        <v>399</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>7</v>
@@ -7694,41 +8035,42 @@
       <c r="E82" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="F82" s="2">
+        <v>4</v>
+      </c>
       <c r="G82" s="2">
-        <v>1866</v>
+        <v>1962</v>
       </c>
       <c r="H82" s="2">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="3" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>811</v>
-      </c>
+        <v>818</v>
+      </c>
+      <c r="M82" s="3"/>
       <c r="N82" s="3" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="O82" s="5">
         <v>46147</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -7736,39 +8078,42 @@
       <c r="E83" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="F83" s="2">
+        <v>9</v>
+      </c>
       <c r="G83" s="2">
-        <v>1869</v>
+        <v>1878</v>
       </c>
       <c r="H83" s="2">
-        <v>1962</v>
+        <v>1984</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="3" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="O83" s="5">
         <v>46147</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>826</v>
+        <v>78</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>7</v>
@@ -7776,31 +8121,34 @@
       <c r="E84" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="F84" s="2">
+        <v>13</v>
+      </c>
       <c r="G84" s="2">
-        <v>1857</v>
+        <v>1907</v>
       </c>
       <c r="H84" s="2">
-        <v>1962</v>
+        <v>1977</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3" t="s">
-        <v>827</v>
+        <v>639</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>829</v>
+        <v>626</v>
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="O84" s="5">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>645</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>174</v>
       </c>
@@ -7833,24 +8181,24 @@
         <v>622</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>637</v>
+        <v>1169</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>623</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>7</v>
@@ -7859,41 +8207,43 @@
         <v>431</v>
       </c>
       <c r="F86" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G86" s="2">
         <v>1970</v>
       </c>
       <c r="H86" s="2">
-        <v>1983</v>
+        <v>2025</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J86" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="K86" s="3" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>7</v>
@@ -7901,42 +8251,38 @@
       <c r="E87" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="F87" s="2">
-        <v>2</v>
-      </c>
       <c r="G87" s="2">
-        <v>1959</v>
-      </c>
-      <c r="H87" s="2">
         <v>1983</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="J87" s="3"/>
       <c r="K87" s="3" t="s">
-        <v>659</v>
+        <v>281</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="M87" s="3"/>
+        <v>795</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>794</v>
+      </c>
       <c r="N87" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>793</v>
+      </c>
+      <c r="O87" s="4">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>7</v>
@@ -7945,43 +8291,41 @@
         <v>431</v>
       </c>
       <c r="F88" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G88" s="2">
-        <v>1986</v>
+        <v>1959</v>
       </c>
       <c r="H88" s="2">
-        <v>2010</v>
+        <v>1983</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J88" s="3"/>
       <c r="K88" s="3" t="s">
-        <v>683</v>
+        <v>658</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>707</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="M88" s="3"/>
       <c r="N88" s="3" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>7</v>
@@ -7990,43 +8334,41 @@
         <v>431</v>
       </c>
       <c r="F89" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2">
         <v>1970</v>
       </c>
       <c r="H89" s="2">
-        <v>2025</v>
+        <v>1983</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="J89" s="3"/>
       <c r="K89" s="3" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="3" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>7</v>
@@ -8034,30 +8376,36 @@
       <c r="E90" s="2" t="s">
         <v>431</v>
       </c>
+      <c r="F90" s="2">
+        <v>3</v>
+      </c>
       <c r="G90" s="2">
-        <v>1983</v>
+        <v>1986</v>
+      </c>
+      <c r="H90" s="2">
+        <v>2010</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="J90" s="3"/>
       <c r="K90" s="3" t="s">
-        <v>281</v>
+        <v>682</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>802</v>
+        <v>677</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>801</v>
+        <v>706</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="O90" s="4">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>701</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>179</v>
       </c>
@@ -8094,10 +8442,10 @@
         <v>475</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>188</v>
       </c>
@@ -8134,10 +8482,10 @@
         <v>476</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>224</v>
       </c>
@@ -8174,10 +8522,10 @@
         <v>477</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>158</v>
       </c>
@@ -8214,10 +8562,10 @@
         <v>478</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>230</v>
       </c>
@@ -8254,10 +8602,10 @@
         <v>479</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>161</v>
       </c>
@@ -8294,10 +8642,10 @@
         <v>480</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>234</v>
       </c>
@@ -8334,10 +8682,10 @@
         <v>481</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>235</v>
       </c>
@@ -8374,10 +8722,10 @@
         <v>482</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>237</v>
       </c>
@@ -8414,10 +8762,10 @@
         <v>483</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>163</v>
       </c>
@@ -8454,10 +8802,10 @@
         <v>485</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>244</v>
       </c>
@@ -8494,10 +8842,10 @@
         <v>484</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>164</v>
       </c>
@@ -8534,10 +8882,10 @@
         <v>486</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>248</v>
       </c>
@@ -8574,10 +8922,10 @@
         <v>487</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>165</v>
       </c>
@@ -8614,10 +8962,10 @@
         <v>489</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>249</v>
       </c>
@@ -8654,10 +9002,10 @@
         <v>488</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>250</v>
       </c>
@@ -8694,10 +9042,10 @@
         <v>490</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>254</v>
       </c>
@@ -8734,10 +9082,10 @@
         <v>492</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>253</v>
       </c>
@@ -8774,10 +9122,10 @@
         <v>491</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>258</v>
       </c>
@@ -8814,18 +9162,18 @@
         <v>474</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -8834,39 +9182,40 @@
         <v>154</v>
       </c>
       <c r="F110" s="2">
-        <v>1</v>
-      </c>
-      <c r="G110" s="2">
-        <v>1962</v>
+        <v>18</v>
       </c>
       <c r="H110" s="2">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
+      <c r="J110" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>523</v>
+      </c>
       <c r="L110" s="3" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3" t="s">
-        <v>553</v>
+        <v>474</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>247</v>
+        <v>177</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>374</v>
+        <v>294</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -8875,41 +9224,41 @@
         <v>154</v>
       </c>
       <c r="F111" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G111" s="2">
-        <v>1933</v>
+        <v>1954</v>
       </c>
       <c r="H111" s="2">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J111" s="3"/>
       <c r="K111" s="3" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="M111" s="3"/>
       <c r="N111" s="3" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -8917,42 +9266,37 @@
       <c r="E112" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F112" s="2">
-        <v>3</v>
-      </c>
       <c r="G112" s="2">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="H112" s="2">
-        <v>1971</v>
+        <v>1954</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J112" s="3"/>
-      <c r="K112" s="3" t="s">
-        <v>549</v>
-      </c>
+      <c r="K112" s="3"/>
       <c r="L112" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="3" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>7</v>
@@ -8960,42 +9304,39 @@
       <c r="E113" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F113" s="2">
-        <v>4</v>
-      </c>
       <c r="G113" s="2">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H113" s="2">
-        <v>1976</v>
+        <v>1953</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J113" s="3"/>
       <c r="K113" s="3" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="3" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>328</v>
+        <v>383</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>7</v>
@@ -9004,40 +9345,41 @@
         <v>154</v>
       </c>
       <c r="F114" s="2">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1867</v>
       </c>
       <c r="H114" s="2">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J114" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="J114" s="3"/>
       <c r="K114" s="3" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="M114" s="3"/>
       <c r="N114" s="3" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>7</v>
@@ -9046,40 +9388,41 @@
         <v>154</v>
       </c>
       <c r="F115" s="2">
-        <v>6</v>
+        <v>15</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1871</v>
       </c>
       <c r="H115" s="2">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J115" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="J115" s="3"/>
       <c r="K115" s="3" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="3" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>7</v>
@@ -9088,41 +9431,41 @@
         <v>154</v>
       </c>
       <c r="F116" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G116" s="2">
-        <v>1940</v>
+        <v>1946</v>
       </c>
       <c r="H116" s="2">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J116" s="3"/>
       <c r="K116" s="3" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="M116" s="3"/>
       <c r="N116" s="3" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>168</v>
+        <v>217</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>7</v>
@@ -9130,42 +9473,39 @@
       <c r="E117" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F117" s="2">
-        <v>8</v>
-      </c>
       <c r="G117" s="2">
-        <v>1931</v>
+        <v>1868</v>
       </c>
       <c r="H117" s="2">
-        <v>1971</v>
+        <v>1946</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J117" s="3"/>
       <c r="K117" s="3" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
       <c r="M117" s="3"/>
       <c r="N117" s="3" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -9174,41 +9514,41 @@
         <v>154</v>
       </c>
       <c r="F118" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G118" s="2">
-        <v>1866</v>
+        <v>1874</v>
       </c>
       <c r="H118" s="2">
-        <v>1970</v>
+        <v>1966</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J118" s="3"/>
       <c r="K118" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>502</v>
+        <v>560</v>
       </c>
       <c r="M118" s="3"/>
       <c r="N118" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>7</v>
@@ -9217,41 +9557,40 @@
         <v>154</v>
       </c>
       <c r="F119" s="2">
-        <v>10</v>
-      </c>
-      <c r="G119" s="2">
-        <v>1858</v>
+        <v>17</v>
       </c>
       <c r="H119" s="2">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J119" s="3"/>
+      <c r="J119" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="K119" s="3" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="3" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>7</v>
@@ -9259,42 +9598,39 @@
       <c r="E120" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F120" s="2">
-        <v>11</v>
-      </c>
       <c r="G120" s="2">
-        <v>1868</v>
+        <v>1873</v>
       </c>
       <c r="H120" s="2">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J120" s="3"/>
       <c r="K120" s="3" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="M120" s="3"/>
       <c r="N120" s="3" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>341</v>
+        <v>388</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>7</v>
@@ -9303,41 +9639,41 @@
         <v>154</v>
       </c>
       <c r="F121" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G121" s="2">
-        <v>1964</v>
+        <v>1866</v>
       </c>
       <c r="H121" s="2">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J121" s="3"/>
       <c r="K121" s="3" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="M121" s="3"/>
       <c r="N121" s="3" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>393</v>
+        <v>313</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>7</v>
@@ -9346,41 +9682,41 @@
         <v>154</v>
       </c>
       <c r="F122" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G122" s="2">
-        <v>1863</v>
+        <v>1856</v>
       </c>
       <c r="H122" s="2">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J122" s="3"/>
       <c r="K122" s="3" t="s">
-        <v>541</v>
+        <v>473</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>501</v>
+        <v>434</v>
       </c>
       <c r="M122" s="3"/>
       <c r="N122" s="3" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>7</v>
@@ -9388,42 +9724,39 @@
       <c r="E123" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F123" s="2">
-        <v>14</v>
-      </c>
       <c r="G123" s="2">
-        <v>1946</v>
+        <v>1876</v>
       </c>
       <c r="H123" s="2">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J123" s="3"/>
       <c r="K123" s="3" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="M123" s="3"/>
       <c r="N123" s="3" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>7</v>
@@ -9432,41 +9765,41 @@
         <v>154</v>
       </c>
       <c r="F124" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G124" s="2">
-        <v>1871</v>
+        <v>1877</v>
       </c>
       <c r="H124" s="2">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J124" s="3"/>
       <c r="K124" s="3" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="M124" s="3"/>
       <c r="N124" s="3" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>294</v>
+        <v>390</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>7</v>
@@ -9475,41 +9808,41 @@
         <v>154</v>
       </c>
       <c r="F125" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G125" s="2">
-        <v>1954</v>
+        <v>1853</v>
       </c>
       <c r="H125" s="2">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J125" s="3"/>
       <c r="K125" s="3" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="M125" s="3"/>
       <c r="N125" s="3" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>361</v>
+        <v>321</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>7</v>
@@ -9518,40 +9851,40 @@
         <v>154</v>
       </c>
       <c r="F126" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H126" s="2">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="M126" s="3"/>
       <c r="N126" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>7</v>
@@ -9559,33 +9892,31 @@
       <c r="E127" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F127" s="2">
-        <v>18</v>
+      <c r="G127" s="2">
+        <v>1869</v>
       </c>
       <c r="H127" s="2">
-        <v>1967</v>
+        <v>1933</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J127" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J127" s="3"/>
       <c r="K127" s="3" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="M127" s="3"/>
       <c r="N127" s="3" t="s">
-        <v>474</v>
+        <v>568</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>240</v>
       </c>
@@ -9625,18 +9956,18 @@
         <v>569</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>229</v>
+        <v>162</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>389</v>
+        <v>328</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>7</v>
@@ -9645,41 +9976,40 @@
         <v>154</v>
       </c>
       <c r="F129" s="2">
-        <v>20</v>
-      </c>
-      <c r="G129" s="2">
-        <v>1877</v>
+        <v>5</v>
       </c>
       <c r="H129" s="2">
-        <v>1966</v>
+        <v>1973</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J129" s="3"/>
+      <c r="J129" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="K129" s="3" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="M129" s="3"/>
       <c r="N129" s="3" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>7</v>
@@ -9688,41 +10018,41 @@
         <v>154</v>
       </c>
       <c r="F130" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G130" s="2">
-        <v>1874</v>
+        <v>1863</v>
       </c>
       <c r="H130" s="2">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J130" s="3"/>
       <c r="K130" s="3" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>560</v>
+        <v>501</v>
       </c>
       <c r="M130" s="3"/>
       <c r="N130" s="3" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>7</v>
@@ -9731,41 +10061,41 @@
         <v>154</v>
       </c>
       <c r="F131" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G131" s="2">
-        <v>1867</v>
+        <v>1933</v>
       </c>
       <c r="H131" s="2">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J131" s="3"/>
       <c r="K131" s="3" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>313</v>
+        <v>396</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -9773,42 +10103,39 @@
       <c r="E132" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F132" s="2">
-        <v>23</v>
-      </c>
       <c r="G132" s="2">
-        <v>1856</v>
+        <v>1865</v>
       </c>
       <c r="H132" s="2">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3" t="s">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>434</v>
+        <v>512</v>
       </c>
       <c r="M132" s="3"/>
       <c r="N132" s="3" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="O132" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>7</v>
@@ -9816,37 +10143,42 @@
       <c r="E133" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F133" s="2">
+        <v>10</v>
+      </c>
       <c r="G133" s="2">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="H133" s="2">
-        <v>1954</v>
+        <v>1969</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J133" s="3"/>
-      <c r="K133" s="3"/>
+      <c r="K133" s="3" t="s">
+        <v>543</v>
+      </c>
       <c r="L133" s="3" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="M133" s="3"/>
       <c r="N133" s="3" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="O133" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>7</v>
@@ -9855,38 +10187,38 @@
         <v>154</v>
       </c>
       <c r="G134" s="2">
-        <v>1852</v>
+        <v>1833</v>
       </c>
       <c r="H134" s="2">
-        <v>1953</v>
+        <v>1962</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J134" s="3"/>
       <c r="K134" s="3" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M134" s="3"/>
       <c r="N134" s="3" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>7</v>
@@ -9894,39 +10226,40 @@
       <c r="E135" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F135" s="2">
+        <v>1</v>
+      </c>
       <c r="G135" s="2">
-        <v>1868</v>
+        <v>1962</v>
       </c>
       <c r="H135" s="2">
-        <v>1946</v>
+        <v>1972</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J135" s="3"/>
-      <c r="K135" s="3" t="s">
-        <v>528</v>
-      </c>
+      <c r="K135" s="3"/>
       <c r="L135" s="3" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="M135" s="3"/>
       <c r="N135" s="3" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="O135" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>387</v>
+        <v>341</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>7</v>
@@ -9934,39 +10267,42 @@
       <c r="E136" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F136" s="2">
+        <v>12</v>
+      </c>
       <c r="G136" s="2">
-        <v>1873</v>
+        <v>1964</v>
       </c>
       <c r="H136" s="2">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J136" s="3"/>
       <c r="K136" s="3" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M136" s="3"/>
       <c r="N136" s="3" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>317</v>
+        <v>398</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>7</v>
@@ -9974,39 +10310,42 @@
       <c r="E137" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F137" s="2">
+        <v>11</v>
+      </c>
       <c r="G137" s="2">
-        <v>1876</v>
+        <v>1868</v>
       </c>
       <c r="H137" s="2">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J137" s="3"/>
       <c r="K137" s="3" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="M137" s="3"/>
       <c r="N137" s="3" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>7</v>
@@ -10014,39 +10353,42 @@
       <c r="E138" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F138" s="2">
+        <v>3</v>
+      </c>
       <c r="G138" s="2">
-        <v>1869</v>
+        <v>1852</v>
       </c>
       <c r="H138" s="2">
-        <v>1933</v>
+        <v>1971</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J138" s="3"/>
       <c r="K138" s="3" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="M138" s="3"/>
       <c r="N138" s="3" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>396</v>
+        <v>343</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>7</v>
@@ -10054,39 +10396,42 @@
       <c r="E139" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F139" s="2">
+        <v>8</v>
+      </c>
       <c r="G139" s="2">
-        <v>1865</v>
+        <v>1931</v>
       </c>
       <c r="H139" s="2">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J139" s="3"/>
       <c r="K139" s="3" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>512</v>
+        <v>579</v>
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>7</v>
@@ -10094,31 +10439,34 @@
       <c r="E140" s="2" t="s">
         <v>154</v>
       </c>
+      <c r="F140" s="2">
+        <v>7</v>
+      </c>
       <c r="G140" s="2">
-        <v>1833</v>
+        <v>1940</v>
       </c>
       <c r="H140" s="2">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>141</v>
       </c>
       <c r="J140" s="3"/>
       <c r="K140" s="3" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="M140" s="3"/>
       <c r="N140" s="3" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>270</v>
       </c>
@@ -10155,18 +10503,18 @@
         <v>581</v>
       </c>
       <c r="O141" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>7</v>
@@ -10175,41 +10523,41 @@
         <v>151</v>
       </c>
       <c r="F142" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G142" s="2">
-        <v>1938</v>
+        <v>1870</v>
       </c>
       <c r="H142" s="2">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J142" s="3"/>
       <c r="K142" s="3" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M142" s="3"/>
       <c r="N142" s="3" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="O142" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>7</v>
@@ -10217,42 +10565,39 @@
       <c r="E143" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F143" s="2">
-        <v>2</v>
-      </c>
       <c r="G143" s="2">
-        <v>1906</v>
+        <v>1946</v>
       </c>
       <c r="H143" s="2">
-        <v>1975</v>
+        <v>1955</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="M143" s="3"/>
       <c r="N143" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="O143" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>7</v>
@@ -10261,10 +10606,10 @@
         <v>151</v>
       </c>
       <c r="F144" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G144" s="2">
-        <v>1906</v>
+        <v>1855</v>
       </c>
       <c r="H144" s="2">
         <v>1975</v>
@@ -10274,28 +10619,28 @@
       </c>
       <c r="J144" s="3"/>
       <c r="K144" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="M144" s="3"/>
       <c r="N144" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
@@ -10304,41 +10649,41 @@
         <v>151</v>
       </c>
       <c r="F145" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G145" s="2">
-        <v>1955</v>
+        <v>1906</v>
       </c>
       <c r="H145" s="2">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J145" s="3"/>
       <c r="K145" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="M145" s="3"/>
       <c r="N145" s="3" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="O145" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>371</v>
+        <v>300</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -10347,10 +10692,10 @@
         <v>151</v>
       </c>
       <c r="F146" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G146" s="2">
-        <v>1855</v>
+        <v>1906</v>
       </c>
       <c r="H146" s="2">
         <v>1975</v>
@@ -10360,28 +10705,28 @@
       </c>
       <c r="J146" s="3"/>
       <c r="K146" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M146" s="3"/>
       <c r="N146" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O146" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>7</v>
@@ -10390,41 +10735,41 @@
         <v>151</v>
       </c>
       <c r="F147" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G147" s="2">
-        <v>1870</v>
+        <v>1938</v>
       </c>
       <c r="H147" s="2">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L147" s="3" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="M147" s="3"/>
       <c r="N147" s="3" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="O147" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>7</v>
@@ -10432,42 +10777,39 @@
       <c r="E148" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F148" s="2">
-        <v>7</v>
-      </c>
       <c r="G148" s="2">
-        <v>1965</v>
+        <v>1855</v>
       </c>
       <c r="H148" s="2">
-        <v>1974</v>
+        <v>1938</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="J148" s="3"/>
       <c r="K148" s="3" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>493</v>
+        <v>590</v>
       </c>
       <c r="M148" s="3"/>
       <c r="N148" s="3" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="O148" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>7</v>
@@ -10476,38 +10818,38 @@
         <v>151</v>
       </c>
       <c r="G149" s="2">
+        <v>1909</v>
+      </c>
+      <c r="H149" s="2">
         <v>1946</v>
-      </c>
-      <c r="H149" s="2">
-        <v>1955</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>122</v>
       </c>
       <c r="J149" s="3"/>
       <c r="K149" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="O149" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>7</v>
@@ -10516,38 +10858,40 @@
         <v>151</v>
       </c>
       <c r="G150" s="2">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="H150" s="2">
-        <v>1938</v>
+        <v>1966</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J150" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="K150" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="M150" s="3"/>
       <c r="N150" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="O150" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>7</v>
@@ -10555,39 +10899,42 @@
       <c r="E151" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="F151" s="2">
+        <v>7</v>
+      </c>
       <c r="G151" s="2">
-        <v>1909</v>
+        <v>1965</v>
       </c>
       <c r="H151" s="2">
-        <v>1946</v>
+        <v>1974</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J151" s="3"/>
       <c r="K151" s="3" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>588</v>
+        <v>493</v>
       </c>
       <c r="M151" s="3"/>
       <c r="N151" s="3" t="s">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>7</v>
@@ -10595,33 +10942,34 @@
       <c r="E152" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="F152" s="2">
+        <v>4</v>
+      </c>
       <c r="G152" s="2">
-        <v>1850</v>
+        <v>1955</v>
       </c>
       <c r="H152" s="2">
-        <v>1966</v>
+        <v>1974</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J152" s="3" t="s">
-        <v>145</v>
-      </c>
+      <c r="J152" s="3"/>
       <c r="K152" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="M152" s="3"/>
       <c r="N152" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>263</v>
       </c>
@@ -10658,10 +11006,10 @@
         <v>619</v>
       </c>
       <c r="O153" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>268</v>
       </c>
@@ -10698,10 +11046,10 @@
         <v>619</v>
       </c>
       <c r="O154" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>202</v>
       </c>
@@ -10728,20 +11076,20 @@
       </c>
       <c r="J155" s="3"/>
       <c r="K155" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M155" s="3"/>
       <c r="N155" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="O155" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>203</v>
       </c>
@@ -10768,20 +11116,20 @@
       </c>
       <c r="J156" s="3"/>
       <c r="K156" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L156" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="M156" s="3"/>
       <c r="N156" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O156" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>204</v>
       </c>
@@ -10808,20 +11156,20 @@
       </c>
       <c r="J157" s="3"/>
       <c r="K157" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M157" s="3"/>
       <c r="N157" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="O157" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>205</v>
       </c>
@@ -10848,20 +11196,20 @@
       </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M158" s="3"/>
       <c r="N158" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="O158" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>206</v>
       </c>
@@ -10888,20 +11236,20 @@
       </c>
       <c r="J159" s="3"/>
       <c r="K159" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M159" s="3"/>
       <c r="N159" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="O159" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>208</v>
       </c>
@@ -10928,20 +11276,20 @@
       </c>
       <c r="J160" s="3"/>
       <c r="K160" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M160" s="3"/>
       <c r="N160" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="O160" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>209</v>
       </c>
@@ -10968,20 +11316,20 @@
       </c>
       <c r="J161" s="3"/>
       <c r="K161" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L161" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M161" s="3"/>
       <c r="N161" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="O161" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>259</v>
       </c>
@@ -11008,28 +11356,28 @@
       </c>
       <c r="J162" s="3"/>
       <c r="K162" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M162" s="3"/>
       <c r="N162" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O162" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>340</v>
+        <v>297</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>7</v>
@@ -11037,42 +11385,39 @@
       <c r="E163" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F163" s="2">
-        <v>1</v>
-      </c>
       <c r="G163" s="2">
-        <v>1935</v>
+        <v>1854</v>
       </c>
       <c r="H163" s="2">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J163" s="3"/>
       <c r="K163" s="3" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="L163" s="3" t="s">
         <v>670</v>
       </c>
       <c r="M163" s="3"/>
       <c r="N163" s="3" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="O163" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>397</v>
+        <v>298</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>7</v>
@@ -11081,32 +11426,33 @@
         <v>152</v>
       </c>
       <c r="F164" s="2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="G164" s="2">
+        <v>1946</v>
       </c>
       <c r="H164" s="2">
-        <v>1986</v>
+        <v>1996</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J164" s="3" t="s">
-        <v>143</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="J164" s="3"/>
       <c r="K164" s="3" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M164" s="3"/>
       <c r="N164" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="O164" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="O164" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>215</v>
       </c>
@@ -11136,28 +11482,28 @@
       </c>
       <c r="J165" s="3"/>
       <c r="K165" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="O165" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>7</v>
@@ -11165,42 +11511,39 @@
       <c r="E166" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F166" s="2">
-        <v>4</v>
-      </c>
       <c r="G166" s="2">
-        <v>1946</v>
+        <v>1882</v>
       </c>
       <c r="H166" s="2">
-        <v>1996</v>
+        <v>1974</v>
       </c>
       <c r="I166" s="2" t="s">
         <v>121</v>
       </c>
       <c r="J166" s="3"/>
       <c r="K166" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L166" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M166" s="3"/>
       <c r="N166" s="3" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="O166" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>7</v>
@@ -11208,39 +11551,36 @@
       <c r="E167" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G167" s="2">
-        <v>1854</v>
-      </c>
       <c r="H167" s="2">
-        <v>1985</v>
+        <v>1968</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J167" s="3"/>
-      <c r="K167" s="3" t="s">
-        <v>679</v>
-      </c>
+      <c r="J167" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K167" s="3"/>
       <c r="L167" s="3" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="M167" s="3"/>
       <c r="N167" s="3" t="s">
-        <v>687</v>
+        <v>553</v>
       </c>
       <c r="O167" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>7</v>
@@ -11248,39 +11588,36 @@
       <c r="E168" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G168" s="2">
-        <v>1882</v>
-      </c>
       <c r="H168" s="2">
-        <v>1974</v>
+        <v>1980</v>
       </c>
       <c r="I168" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J168" s="3"/>
-      <c r="K168" s="3" t="s">
-        <v>682</v>
-      </c>
+      <c r="J168" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K168" s="3"/>
       <c r="L168" s="3" t="s">
         <v>676</v>
       </c>
       <c r="M168" s="3"/>
       <c r="N168" s="3" t="s">
-        <v>700</v>
+        <v>553</v>
       </c>
       <c r="O168" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>7</v>
@@ -11288,36 +11625,42 @@
       <c r="E169" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="F169" s="2">
+        <v>1</v>
+      </c>
+      <c r="G169" s="2">
+        <v>1935</v>
+      </c>
       <c r="H169" s="2">
-        <v>1968</v>
+        <v>1986</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J169" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K169" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3" t="s">
+        <v>683</v>
+      </c>
       <c r="L169" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="M169" s="3"/>
       <c r="N169" s="3" t="s">
-        <v>553</v>
+        <v>702</v>
       </c>
       <c r="O169" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>7</v>
@@ -11325,36 +11668,39 @@
       <c r="E170" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="G170" s="2">
+        <v>1850</v>
+      </c>
       <c r="H170" s="2">
-        <v>1980</v>
+        <v>1935</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J170" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K170" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="J170" s="3"/>
+      <c r="K170" s="3" t="s">
+        <v>685</v>
+      </c>
       <c r="L170" s="3" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="M170" s="3"/>
       <c r="N170" s="3" t="s">
-        <v>553</v>
+        <v>703</v>
       </c>
       <c r="O170" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>7</v>
@@ -11362,37 +11708,411 @@
       <c r="E171" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G171" s="2">
-        <v>1850</v>
+      <c r="F171" s="2">
+        <v>2</v>
       </c>
       <c r="H171" s="2">
-        <v>1935</v>
+        <v>1986</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J171" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="K171" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="L171" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M171" s="3"/>
       <c r="N171" s="3" t="s">
         <v>704</v>
       </c>
       <c r="O171" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G172" s="2">
+        <v>1954</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="J172" s="3"/>
-      <c r="K172" s="3"/>
+      <c r="K172" s="3" t="s">
+        <v>1170</v>
+      </c>
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
       <c r="O172" s="3"/>
+    </row>
+    <row r="173" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G173" s="2">
+        <v>1850</v>
+      </c>
+      <c r="H173" s="2">
+        <v>1954</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="3"/>
+      <c r="M173" s="3"/>
+      <c r="N173" s="3"/>
+      <c r="O173" s="3"/>
+    </row>
+    <row r="174" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G174" s="2">
+        <v>1973</v>
+      </c>
+      <c r="H174" s="2">
+        <v>1996</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="3"/>
+      <c r="M174" s="3"/>
+      <c r="N174" s="3"/>
+      <c r="O174" s="3"/>
+    </row>
+    <row r="175" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G175" s="2">
+        <v>1972</v>
+      </c>
+      <c r="H175" s="2">
+        <v>1973</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J175" s="3"/>
+      <c r="K175" s="3"/>
+      <c r="L175" s="3"/>
+      <c r="M175" s="3"/>
+      <c r="N175" s="3"/>
+      <c r="O175" s="3"/>
+    </row>
+    <row r="176" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H176" s="2">
+        <v>1972</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J176" s="3"/>
+      <c r="K176" s="3"/>
+      <c r="L176" s="3"/>
+      <c r="M176" s="3"/>
+      <c r="N176" s="3"/>
+      <c r="O176" s="3"/>
+    </row>
+    <row r="177" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H177" s="2">
+        <v>1982</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J177" s="3"/>
+      <c r="K177" s="3"/>
+      <c r="L177" s="3"/>
+      <c r="M177" s="3"/>
+      <c r="N177" s="3"/>
+      <c r="O177" s="3"/>
+    </row>
+    <row r="178" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G178" s="2">
+        <v>1946</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J178" s="3"/>
+      <c r="K178" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L178" s="3"/>
+      <c r="M178" s="3"/>
+      <c r="N178" s="3"/>
+      <c r="O178" s="3"/>
+    </row>
+    <row r="179" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G179" s="2">
+        <v>1856</v>
+      </c>
+      <c r="H179" s="2">
+        <v>1946</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J179" s="3"/>
+      <c r="K179" s="3"/>
+      <c r="L179" s="3"/>
+      <c r="M179" s="3"/>
+      <c r="N179" s="3"/>
+      <c r="O179" s="3"/>
+    </row>
+    <row r="180" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G180" s="2">
+        <v>1891</v>
+      </c>
+      <c r="H180" s="2">
+        <v>1946</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J180" s="3"/>
+      <c r="K180" s="3"/>
+      <c r="L180" s="3"/>
+      <c r="M180" s="3"/>
+      <c r="N180" s="3"/>
+      <c r="O180" s="3"/>
+    </row>
+    <row r="181" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="G181" s="2">
+        <v>1948</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J181" s="3"/>
+      <c r="K181" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L181" s="3"/>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3"/>
+      <c r="O181" s="3"/>
+    </row>
+    <row r="182" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="G182" s="2">
+        <v>1857</v>
+      </c>
+      <c r="H182" s="2">
+        <v>1948</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J182" s="3"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3"/>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3"/>
+      <c r="O182" s="3"/>
+    </row>
+    <row r="183" spans="1:15" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="G183" s="2">
+        <v>1980</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J183" s="3"/>
+      <c r="K183" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="L183" s="3"/>
+      <c r="M183" s="3"/>
+      <c r="N183" s="3"/>
+      <c r="O183" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -11405,7 +12125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C86150-5091-49F7-9076-DE8E67A7DBD0}">
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr defaultColWidth="35" defaultRowHeight="29" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.26953125" style="2" customWidth="1"/>
@@ -13103,10 +13823,10 @@
         <v>170</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E113" s="3"/>
     </row>
@@ -13115,13 +13835,13 @@
         <v>1997</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="E114" s="3"/>
     </row>
@@ -13130,10 +13850,10 @@
         <v>2005</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>174</v>
@@ -13148,10 +13868,10 @@
         <v>171</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E116" s="3"/>
     </row>
@@ -13163,10 +13883,10 @@
         <v>171</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E117" s="3"/>
     </row>
@@ -13178,10 +13898,10 @@
         <v>171</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E118" s="3"/>
     </row>
@@ -13193,10 +13913,10 @@
         <v>171</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E119" s="3"/>
     </row>
@@ -13208,10 +13928,10 @@
         <v>171</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="E120" s="3"/>
     </row>
@@ -13223,10 +13943,10 @@
         <v>170</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="E121" s="3"/>
     </row>
@@ -13238,10 +13958,10 @@
         <v>171</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E122" s="3"/>
     </row>
@@ -13253,10 +13973,10 @@
         <v>170</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="E123" s="3"/>
     </row>
@@ -13268,10 +13988,10 @@
         <v>171</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E124" s="3"/>
     </row>
@@ -13283,10 +14003,10 @@
         <v>171</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E125" s="3"/>
     </row>
@@ -13298,10 +14018,10 @@
         <v>171</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E126" s="3"/>
     </row>
@@ -13313,10 +14033,10 @@
         <v>171</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E127" s="3"/>
     </row>
@@ -13328,10 +14048,10 @@
         <v>172</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="E128" s="3"/>
     </row>
@@ -13343,10 +14063,10 @@
         <v>172</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="E129" s="3"/>
     </row>
@@ -13358,10 +14078,10 @@
         <v>171</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E130" s="3"/>
     </row>
@@ -13373,10 +14093,10 @@
         <v>170</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="E131" s="3"/>
     </row>
@@ -13388,10 +14108,10 @@
         <v>171</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E132" s="3"/>
     </row>
@@ -13403,10 +14123,10 @@
         <v>171</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E133" s="3"/>
     </row>
@@ -13418,10 +14138,10 @@
         <v>171</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E134" s="3"/>
     </row>
@@ -13433,10 +14153,10 @@
         <v>171</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E135" s="3"/>
     </row>
@@ -13448,10 +14168,10 @@
         <v>172</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="E136" s="3"/>
     </row>
@@ -13463,10 +14183,10 @@
         <v>172</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="E137" s="3"/>
     </row>
@@ -13478,10 +14198,10 @@
         <v>171</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E138" s="3"/>
     </row>
@@ -13493,10 +14213,10 @@
         <v>171</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E139" s="3"/>
     </row>
@@ -13508,10 +14228,10 @@
         <v>170</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="E140" s="3"/>
     </row>
@@ -13523,10 +14243,10 @@
         <v>171</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E141" s="3"/>
     </row>
@@ -13538,10 +14258,10 @@
         <v>171</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E142" s="3"/>
     </row>
@@ -13553,10 +14273,10 @@
         <v>171</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E143" s="3"/>
     </row>
@@ -13568,327 +14288,447 @@
         <v>171</v>
       </c>
       <c r="C144" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="2">
+        <v>1962</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="2">
+        <v>1972</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="2">
+        <v>1961</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="2">
+        <v>1963</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="2">
+        <v>1974</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="2">
+        <v>1971</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="E144" s="3"/>
-    </row>
-    <row r="145" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="6">
-        <v>1962</v>
-      </c>
-      <c r="B145" s="6" t="s">
+      <c r="D150" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="2">
+        <v>1975</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="2">
+        <v>1963</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C152" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D152" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="E145" s="3"/>
-    </row>
-    <row r="146" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="6">
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="2">
+        <v>1975</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="2">
+        <v>1944</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="2">
+        <v>1968</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="2">
+        <v>1968</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="2">
+        <v>1970</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="2">
+        <v>1978</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="2">
+        <v>1964</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="2">
+        <v>1979</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="2">
+        <v>1951</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="2">
+        <v>1991</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="2">
+        <v>1979</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="2">
+        <v>1987</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="2">
+        <v>1988</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="2">
+        <v>1954</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="2">
+        <v>1996</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="2">
+        <v>1973</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="2">
         <v>1972</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B169" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="2">
+        <v>1946</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="2">
+        <v>1946</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="2">
+        <v>1982</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="6">
-        <v>1961</v>
-      </c>
-      <c r="B147" s="6" t="s">
+      <c r="C172" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="2">
+        <v>1948</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>864</v>
-      </c>
-      <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="6">
-        <v>1963</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>864</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>863</v>
-      </c>
-      <c r="E148" s="3"/>
-    </row>
-    <row r="149" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="6">
-        <v>1974</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>863</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="6">
-        <v>1971</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="E150" s="3"/>
-    </row>
-    <row r="151" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="6">
-        <v>1975</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="6">
-        <v>1963</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>869</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E152" s="3"/>
-    </row>
-    <row r="153" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="6">
-        <v>1975</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="6">
-        <v>1944</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>871</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="6">
-        <v>1968</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="6">
-        <v>1968</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="6">
-        <v>1970</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="E157" s="3"/>
-    </row>
-    <row r="158" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="6">
-        <v>1978</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>874</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="6">
-        <v>1964</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>875</v>
-      </c>
-      <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="6">
-        <v>1979</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>875</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="6">
-        <v>1951</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>878</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>877</v>
-      </c>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="6">
-        <v>1991</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>877</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="6">
-        <v>1979</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>880</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="6">
-        <v>1987</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="6">
-        <v>1988</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>881</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="E165" s="3"/>
+      <c r="C173" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E173" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -13921,7 +14761,7 @@
         <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13932,7 +14772,7 @@
         <v>405</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13943,7 +14783,7 @@
         <v>406</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13954,7 +14794,7 @@
         <v>407</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13965,7 +14805,7 @@
         <v>408</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13976,7 +14816,7 @@
         <v>409</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13987,436 +14827,436 @@
         <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>750</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>751</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>758</v>
+        <v>1141</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>777</v>
+        <v>1142</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>744</v>
+        <v>1145</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>745</v>
+        <v>1146</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>785</v>
+        <v>1147</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>746</v>
+        <v>1144</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>1010</v>
+        <v>1143</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="29" customHeight="1" x14ac:dyDescent="0.35">
